--- a/data/B24_department_schedules_midterms/Makine Mühendisliği.xlsx
+++ b/data/B24_department_schedules_midterms/Makine Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4F3634-4D0E-4475-9DAD-788487569A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{1C4F3634-4D0E-4475-9DAD-788487569A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE344522-CA8D-4733-9D6D-4D75AF6ECB18}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
   <si>
     <t>Year:</t>
   </si>
@@ -268,9 +268,6 @@
     <t>Rooms Used</t>
   </si>
   <si>
-    <t>D201,D204,C211,C212</t>
-  </si>
-  <si>
     <t>D201</t>
   </si>
   <si>
@@ -283,16 +280,49 @@
     <t>D201,D204,C212</t>
   </si>
   <si>
-    <t>Amfi 3, Amfi 4, BB04</t>
-  </si>
-  <si>
-    <t>Amfi 3,Amfi 4,BB04</t>
-  </si>
-  <si>
-    <t>D201,D204</t>
-  </si>
-  <si>
     <t>YLAB 2,CAD1,YLAB 2,CAD1</t>
+  </si>
+  <si>
+    <t>timeslots</t>
+  </si>
+  <si>
+    <t>Amfi 3,BB01,BZ01</t>
+  </si>
+  <si>
+    <t>Amfi 4,BB01</t>
+  </si>
+  <si>
+    <t>Amfi 3,BB04</t>
+  </si>
+  <si>
+    <t>BB04,BB01,BZ01,C212</t>
+  </si>
+  <si>
+    <t>Amfi 3,D201,D204</t>
+  </si>
+  <si>
+    <t>BB01,BB04</t>
+  </si>
+  <si>
+    <t>Amfi 4,BB04</t>
+  </si>
+  <si>
+    <t>D201,D204,C208</t>
+  </si>
+  <si>
+    <t>Amfi 4,Amfi 3</t>
+  </si>
+  <si>
+    <t>D204,C212</t>
+  </si>
+  <si>
+    <t>C212</t>
+  </si>
+  <si>
+    <t>CAD1</t>
+  </si>
+  <si>
+    <t>Amfi 3,BB04,BB01</t>
   </si>
 </sst>
 </file>
@@ -373,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -390,11 +420,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -473,18 +510,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}" name="Table1" displayName="Table1" ref="A1:F39" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F39" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}" name="Table1" displayName="Table1" ref="A1:G39" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G39" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F39">
     <sortCondition ref="B1:B39"/>
   </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1FB3D1C1-309C-4BF7-AD72-258A5E23F6F0}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{13BC1CEB-19D3-463C-8CE2-36FD3B265790}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{9221BBC8-E010-48B8-A24D-0C20CC467181}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{449FCC7C-AF42-4141-BCCE-A671718618CA}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{C8015091-4880-4315-B086-0FB0F0D30CC6}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{8D463A4C-1DB6-43F6-9D9C-71FE833DE817}" name="Rooms Used" dataDxfId="0"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{1FB3D1C1-309C-4BF7-AD72-258A5E23F6F0}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{13BC1CEB-19D3-463C-8CE2-36FD3B265790}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{9221BBC8-E010-48B8-A24D-0C20CC467181}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{449FCC7C-AF42-4141-BCCE-A671718618CA}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C8015091-4880-4315-B086-0FB0F0D30CC6}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{8D463A4C-1DB6-43F6-9D9C-71FE833DE817}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{308F6B3A-6ACD-47BA-8DDA-68614CAC9022}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -777,15 +815,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="33.26953125" customWidth="1"/>
-    <col min="6" max="6" width="42.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="33.265625" customWidth="1"/>
+    <col min="6" max="6" width="42.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,8 +842,11 @@
       <c r="F1" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -813,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2">
         <v>4</v>
@@ -822,10 +863,14 @@
         <v>43</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -836,16 +881,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="G3" s="7">
+        <v>2</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -853,19 +902,23 @@
         <v>6</v>
       </c>
       <c r="C4" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="G4" s="7">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -873,19 +926,23 @@
         <v>7</v>
       </c>
       <c r="C5" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -893,19 +950,22 @@
         <v>8</v>
       </c>
       <c r="C6" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+      <c r="G6" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -913,7 +973,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
@@ -922,10 +982,14 @@
         <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -933,7 +997,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" s="3">
         <v>3</v>
@@ -942,10 +1006,14 @@
         <v>51</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -953,19 +1021,23 @@
         <v>16</v>
       </c>
       <c r="C9" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+      <c r="G9" s="7">
+        <v>5</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -973,19 +1045,23 @@
         <v>11</v>
       </c>
       <c r="C10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -993,19 +1069,22 @@
         <v>15</v>
       </c>
       <c r="C11" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+      <c r="G11" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -1013,19 +1092,22 @@
         <v>12</v>
       </c>
       <c r="C12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="G12" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -1036,16 +1118,19 @@
         <v>1</v>
       </c>
       <c r="D13" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>60</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="G13" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>3</v>
       </c>
@@ -1053,19 +1138,22 @@
         <v>19</v>
       </c>
       <c r="C14" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+      <c r="G14" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -1073,7 +1161,7 @@
         <v>21</v>
       </c>
       <c r="C15" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D15" s="4">
         <v>2</v>
@@ -1082,10 +1170,13 @@
         <v>59</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="G15" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -1093,7 +1184,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D16" s="4">
         <v>3</v>
@@ -1102,10 +1193,13 @@
         <v>55</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="G16" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -1122,10 +1216,13 @@
         <v>56</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+      <c r="G17" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1133,7 +1230,7 @@
         <v>23</v>
       </c>
       <c r="C18" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1142,10 +1239,13 @@
         <v>61</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1153,7 +1253,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -1162,10 +1262,13 @@
         <v>62</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>3</v>
       </c>
@@ -1173,7 +1276,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -1182,10 +1285,13 @@
         <v>58</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="G20" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>4</v>
       </c>
@@ -1193,7 +1299,7 @@
         <v>36</v>
       </c>
       <c r="C21" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -1204,8 +1310,11 @@
       <c r="F21" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <v>4</v>
       </c>
@@ -1213,7 +1322,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" s="5">
         <v>1</v>
@@ -1222,10 +1331,13 @@
         <v>66</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+      <c r="G22" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -1233,7 +1345,7 @@
         <v>26</v>
       </c>
       <c r="C23" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -1242,10 +1354,13 @@
         <v>64</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="G23" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1253,7 +1368,7 @@
         <v>27</v>
       </c>
       <c r="C24" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D24" s="5">
         <v>1</v>
@@ -1262,10 +1377,13 @@
         <v>65</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="G24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>4</v>
       </c>
@@ -1273,7 +1391,7 @@
         <v>37</v>
       </c>
       <c r="C25" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
@@ -1282,10 +1400,13 @@
         <v>75</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>4</v>
       </c>
@@ -1302,10 +1423,13 @@
         <v>79</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="G26" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1313,7 +1437,7 @@
         <v>38</v>
       </c>
       <c r="C27" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
@@ -1324,8 +1448,11 @@
       <c r="F27" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>4</v>
       </c>
@@ -1333,7 +1460,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
@@ -1342,10 +1469,13 @@
         <v>69</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="G28" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>4</v>
       </c>
@@ -1353,7 +1483,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D29" s="5">
         <v>1</v>
@@ -1362,10 +1492,13 @@
         <v>70</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="G29" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -1373,7 +1506,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D30" s="5">
         <v>1</v>
@@ -1384,8 +1517,11 @@
       <c r="F30" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5">
         <v>4</v>
       </c>
@@ -1393,7 +1529,7 @@
         <v>33</v>
       </c>
       <c r="C31" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D31" s="5">
         <v>1</v>
@@ -1402,10 +1538,13 @@
         <v>71</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="G31" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>4</v>
       </c>
@@ -1413,7 +1552,7 @@
         <v>35</v>
       </c>
       <c r="C32" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D32" s="5">
         <v>1</v>
@@ -1424,8 +1563,11 @@
       <c r="F32" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5">
         <v>4</v>
       </c>
@@ -1433,7 +1575,7 @@
         <v>40</v>
       </c>
       <c r="C33" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
@@ -1442,10 +1584,13 @@
         <v>78</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="G33" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="5">
         <v>4</v>
       </c>
@@ -1453,7 +1598,7 @@
         <v>30</v>
       </c>
       <c r="C34" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D34" s="5">
         <v>1</v>
@@ -1464,8 +1609,11 @@
       <c r="F34" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="5">
         <v>4</v>
       </c>
@@ -1473,7 +1621,7 @@
         <v>42</v>
       </c>
       <c r="C35" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D35" s="5">
         <v>1</v>
@@ -1484,8 +1632,11 @@
       <c r="F35" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G35" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="5">
         <v>4</v>
       </c>
@@ -1493,7 +1644,7 @@
         <v>39</v>
       </c>
       <c r="C36" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D36" s="5">
         <v>1</v>
@@ -1504,8 +1655,11 @@
       <c r="F36" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G36" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="5">
         <v>4</v>
       </c>
@@ -1513,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D37" s="5">
         <v>1</v>
@@ -1524,8 +1678,11 @@
       <c r="F37" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G37" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>1</v>
       </c>
@@ -1533,7 +1690,7 @@
         <v>9</v>
       </c>
       <c r="C38" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="2">
         <v>3</v>
@@ -1542,10 +1699,13 @@
         <v>47</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="G38" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="5">
         <v>4</v>
       </c>
@@ -1553,7 +1713,7 @@
         <v>34</v>
       </c>
       <c r="C39" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" s="5">
         <v>1</v>
@@ -1562,7 +1722,10 @@
         <v>72</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="G39" s="7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
